--- a/artfynd/A 47412-2025 artfynd.xlsx
+++ b/artfynd/A 47412-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,6 +808,372 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129501366</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Barrskog SÖ om Långeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>461611</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6409704</v>
+      </c>
+      <c r="S3" t="n">
+        <v>18</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skärstad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129501362</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Barrskog SÖ om Långeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>461611</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6409704</v>
+      </c>
+      <c r="S4" t="n">
+        <v>18</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skärstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129501203</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97182</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>232</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedsäckmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Calypogeia suecica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Barrskog SÖ om Långeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>461589</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6409669</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skärstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mycket gammal murken ved intill bergvägg</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47412-2025 artfynd.xlsx
+++ b/artfynd/A 47412-2025 artfynd.xlsx
@@ -1058,7 +1058,7 @@
         <v>129501203</v>
       </c>
       <c r="B5" t="n">
-        <v>97182</v>
+        <v>97186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47412-2025 artfynd.xlsx
+++ b/artfynd/A 47412-2025 artfynd.xlsx
@@ -1058,7 +1058,7 @@
         <v>129501203</v>
       </c>
       <c r="B5" t="n">
-        <v>97186</v>
+        <v>97194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47412-2025 artfynd.xlsx
+++ b/artfynd/A 47412-2025 artfynd.xlsx
@@ -1058,7 +1058,7 @@
         <v>129501203</v>
       </c>
       <c r="B5" t="n">
-        <v>97194</v>
+        <v>97197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47412-2025 artfynd.xlsx
+++ b/artfynd/A 47412-2025 artfynd.xlsx
@@ -1058,7 +1058,7 @@
         <v>129501203</v>
       </c>
       <c r="B5" t="n">
-        <v>97197</v>
+        <v>97226</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47412-2025 artfynd.xlsx
+++ b/artfynd/A 47412-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1058,7 +1058,7 @@
         <v>129501203</v>
       </c>
       <c r="B5" t="n">
-        <v>97226</v>
+        <v>97238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,6 +1174,123 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129739153</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97023</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>291</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stubbtrådmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fuscocephaloziopsis catenulata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Huebener) Váňa &amp; L.Söderstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Barrskog SÖ om Långeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>461603</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6409662</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skärstad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47412-2025 artfynd.xlsx
+++ b/artfynd/A 47412-2025 artfynd.xlsx
@@ -1058,7 +1058,7 @@
         <v>129501203</v>
       </c>
       <c r="B5" t="n">
-        <v>97238</v>
+        <v>97239</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>129739153</v>
       </c>
       <c r="B6" t="n">
-        <v>97023</v>
+        <v>97024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47412-2025 artfynd.xlsx
+++ b/artfynd/A 47412-2025 artfynd.xlsx
@@ -1058,7 +1058,7 @@
         <v>129501203</v>
       </c>
       <c r="B5" t="n">
-        <v>97239</v>
+        <v>97244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>129739153</v>
       </c>
       <c r="B6" t="n">
-        <v>97024</v>
+        <v>97029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47412-2025 artfynd.xlsx
+++ b/artfynd/A 47412-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1175,123 +1175,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>129739153</v>
-      </c>
-      <c r="B6" t="n">
-        <v>97029</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>291</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Stubbtrådmossa</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Fuscocephaloziopsis catenulata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Huebener) Váňa &amp; L.Söderstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Barrskog SÖ om Långeberg, Sm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>461603</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6409662</v>
-      </c>
-      <c r="S6" t="n">
-        <v>12</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Skärstad</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:12</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:12</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>William Rosén</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>William Rosén</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47412-2025 artfynd.xlsx
+++ b/artfynd/A 47412-2025 artfynd.xlsx
@@ -1058,7 +1058,7 @@
         <v>129501203</v>
       </c>
       <c r="B5" t="n">
-        <v>97244</v>
+        <v>97248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47412-2025 artfynd.xlsx
+++ b/artfynd/A 47412-2025 artfynd.xlsx
@@ -1058,7 +1058,7 @@
         <v>129501203</v>
       </c>
       <c r="B5" t="n">
-        <v>97248</v>
+        <v>97250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47412-2025 artfynd.xlsx
+++ b/artfynd/A 47412-2025 artfynd.xlsx
@@ -1058,7 +1058,7 @@
         <v>129501203</v>
       </c>
       <c r="B5" t="n">
-        <v>97250</v>
+        <v>97260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47412-2025 artfynd.xlsx
+++ b/artfynd/A 47412-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110338711</v>
+        <v>129501203</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,28 +686,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>232</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedsäckmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calypogeia suecica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -720,12 +711,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med groddkorn</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -734,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461592.8796657792</v>
+        <v>461589</v>
       </c>
       <c r="R2" t="n">
-        <v>6409688.589680805</v>
+        <v>6409669</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,27 +750,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I västlig sluttning, i mosstäcke. På kullarna finns äldre skog med gamla tallar och granar.</t>
+          <t>Mycket gammal murken ved intill bergvägg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -811,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129501366</v>
+        <v>129501435</v>
       </c>
       <c r="B3" t="n">
-        <v>4773</v>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,37 +808,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -861,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461611</v>
+        <v>461593</v>
       </c>
       <c r="R3" t="n">
-        <v>6409704</v>
+        <v>6409743</v>
       </c>
       <c r="S3" t="n">
         <v>18</v>
@@ -896,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -906,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129501362</v>
+        <v>129501366</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>4775</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1055,43 +1036,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129501203</v>
+        <v>129501362</v>
       </c>
       <c r="B5" t="n">
-        <v>97260</v>
+        <v>5179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>232</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedsäckmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calypogeia suecica</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1100,13 +1086,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461589</v>
+        <v>461611</v>
       </c>
       <c r="R5" t="n">
-        <v>6409669</v>
+        <v>6409704</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1135,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1145,12 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mycket gammal murken ved intill bergvägg</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,6 +1155,263 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110338711</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Barrskog SÖ om Långeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>461593</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6409689</v>
+      </c>
+      <c r="S6" t="n">
+        <v>14</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skärstad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-06-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-06-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I västlig sluttning, i mosstäcke. På kullarna finns äldre skog med gamla tallar och granar.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110338832</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Barrskog SÖ om Långeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>461599</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6409727</v>
+      </c>
+      <c r="S7" t="n">
+        <v>18</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skärstad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-06-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I västlig sluttning, på liten djurstig.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47412-2025 artfynd.xlsx
+++ b/artfynd/A 47412-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129501203</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129501435</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129501366</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1155,6 +1175,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129501362</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1286,6 +1311,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110338711</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1412,8 +1442,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110338832</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>